--- a/KI_UseCases_Uebersicht.xlsx
+++ b/KI_UseCases_Uebersicht.xlsx
@@ -192,7 +192,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UseCases" displayName="UseCases" ref="A1:F118" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UseCases" displayName="UseCases" ref="A1:F120" headerRowCount="1">
   <autoFilter ref="A1:F118"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Nr."/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4070,6 +4070,66 @@
       <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Research (aimultiple.com)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Tausende inaktive Leads liegen ungenutzt in CRM und Datenbanken; Vertriebsteams haben keine Kapazität, sie systematisch und persönlich erneut anzurufen, dadurch bleiben enorme Umsatzpotenziale liegen</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Voice-Agent Leadreaktivierung: KI-Telefonassistent ruft inaktive Leads automatisiert an, qualifiziert das aktuelle Interesse im natürlichen Gespräch, bucht Termine und übergibt qualifizierte Kontakte zurück ins CRM bzw. an das Vertriebsteam</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Vertrieb</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Kundenkommunikation &amp; Personalisierung</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Recherche/Trend Mai 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Eingehende Leads (Webformular, Messe, Newsletter) enthalten meist nur Name und E-Mail; Vertrieb und Marketing fehlen Kontext (Rolle, Firma, Branche, Größe, Signale), um zu priorisieren und zu personalisieren</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Lead-Enrichment-Agent: KI reichert eingehende Leads automatisch mit öffentlich verfügbaren Daten an (Position, Firmographics, LinkedIn, Branchen-News, Funding-Status) und überträgt das vollständige Profil strukturiert ins CRM</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Vertrieb</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Datenpflege &amp; Stammdaten</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Recherche/Trend Mai 2026</t>
         </is>
       </c>
     </row>

--- a/KI_UseCases_Uebersicht.xlsx
+++ b/KI_UseCases_Uebersicht.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Newslettererstellung und -optimierung ist ressourcenintensiv und wenig datengetrieben</t>
+          <t>Newsletter sind ressourcenintensiv – Themenrecherche, Strukturierung, Layout, Personalisierung pro Zielgruppe, Übersetzung und Versandsteuerung erfordern viele manuelle Schritte; datengetriebene Entscheidungen zu Inhalten und Versandzeitpunkt fehlen, sodass Öffnungs- und Klickraten unter dem Möglichen bleiben</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Aufgaben werden vergessen und Fristen verpasst mangels intelligenter, nutzerorientierter Erinnerungen</t>
+          <t>Aufgaben werden vergessen und Fristen verpasst, weil klassische Reminder pauschal sind und den individuellen Arbeitskontext (Aufgabenpriorität, Tagesablauf, bisherige Erledigungsmuster) nicht berücksichtigen – wichtige To-Dos gehen im Tagesgeschäft unter</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Smart Nudging: KI erkennt To-Do-Muster und setzt kontextbasierte Reminder</t>
+          <t>Smart Nudging: KI analysiert individuelle To-Do-Muster und Erledigungszeiten, identifiziert die richtigen Momente für eine Erinnerung und setzt kontextbezogene, personalisierte Reminder statt pauschaler Benachrichtigungen</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">

--- a/KI_UseCases_Uebersicht.xlsx
+++ b/KI_UseCases_Uebersicht.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Newsletter sind ressourcenintensiv – Themenrecherche, Strukturierung, Layout, Personalisierung pro Zielgruppe, Übersetzung und Versandsteuerung erfordern viele manuelle Schritte; datengetriebene Entscheidungen zu Inhalten und Versandzeitpunkt fehlen, sodass Öffnungs- und Klickraten unter dem Möglichen bleiben</t>
+          <t>Newslettererstellung und -optimierung ist ressourcenintensiv und wenig datengetrieben</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Aufgaben werden vergessen und Fristen verpasst, weil klassische Reminder pauschal sind und den individuellen Arbeitskontext (Aufgabenpriorität, Tagesablauf, bisherige Erledigungsmuster) nicht berücksichtigen – wichtige To-Dos gehen im Tagesgeschäft unter</t>
+          <t>Aufgaben werden vergessen und Fristen verpasst mangels intelligenter, nutzerorientierter Erinnerungen</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Smart Nudging: KI analysiert individuelle To-Do-Muster und Erledigungszeiten, identifiziert die richtigen Momente für eine Erinnerung und setzt kontextbezogene, personalisierte Reminder statt pauschaler Benachrichtigungen</t>
+          <t>Smart Nudging: KI erkennt To-Do-Muster und setzt kontextbasierte Reminder</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
